--- a/data_idhm.xlsx
+++ b/data_idhm.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2BF99F71E552AEC7B4A73C2CDA0DF16B40D8C392" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leona\OneDrive\Documentos\Safety Intelligence (1)\safety_leitor_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC45BEE-7D30-42E8-AC40-E6CDB48B1867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -1104,9 +1109,6 @@
     <t>Nova Independência (SP)</t>
   </si>
   <si>
-    <t>Embu (SP)</t>
-  </si>
-  <si>
     <t>Aspásia (SP)</t>
   </si>
   <si>
@@ -1620,9 +1622,6 @@
     <t>Cajuru (SP)</t>
   </si>
   <si>
-    <t>Florínia (SP)</t>
-  </si>
-  <si>
     <t>Uru (SP)</t>
   </si>
   <si>
@@ -1638,9 +1637,6 @@
     <t>Ribeirão Bonito (SP)</t>
   </si>
   <si>
-    <t>Biritiba-Mirim (SP)</t>
-  </si>
-  <si>
     <t>Barão de Antonina (SP)</t>
   </si>
   <si>
@@ -1830,9 +1826,6 @@
     <t>Caiuá (SP)</t>
   </si>
   <si>
-    <t>São Luís do Paraitinga (SP)</t>
-  </si>
-  <si>
     <t>Potim (SP)</t>
   </si>
   <si>
@@ -1993,13 +1986,25 @@
   </si>
   <si>
     <t>Ribeirão Branco (SP)</t>
+  </si>
+  <si>
+    <t>Embu das Artes (SP)</t>
+  </si>
+  <si>
+    <t>Florínea (SP)</t>
+  </si>
+  <si>
+    <t>Biritiba Mirim (SP)</t>
+  </si>
+  <si>
+    <t>São Luiz do Paraitinga (SP)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2010,6 +2015,13 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2032,9 +2044,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2340,7 +2353,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z646"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -2353,7 +2366,7 @@
     <col min="9" max="9" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2399,7 +2412,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2428,7 +2441,7 @@
         <v>0.88700000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2457,7 +2470,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2486,7 +2499,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2515,7 +2528,7 @@
         <v>0.86599999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2544,7 +2557,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2573,7 +2586,7 @@
         <v>0.878</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2602,7 +2615,7 @@
         <v>0.877</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2631,7 +2644,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2660,7 +2673,7 @@
         <v>0.84899999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -2689,7 +2702,7 @@
         <v>0.871</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2718,7 +2731,7 @@
         <v>0.876</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2747,7 +2760,7 @@
         <v>0.85499999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2776,7 +2789,7 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -2805,7 +2818,7 @@
         <v>0.85499999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2834,7 +2847,7 @@
         <v>0.86499999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -2863,7 +2876,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2892,7 +2905,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2921,7 +2934,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2950,7 +2963,7 @@
         <v>0.86199999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2979,7 +2992,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3008,7 +3021,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3037,7 +3050,7 @@
         <v>0.88300000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3066,7 +3079,7 @@
         <v>0.86899999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3095,7 +3108,7 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3124,7 +3137,7 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -3153,7 +3166,7 @@
         <v>0.88600000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -3182,7 +3195,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -3211,7 +3224,7 @@
         <v>0.871</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -3240,7 +3253,7 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -3269,7 +3282,7 @@
         <v>0.872</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -3298,7 +3311,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -3327,7 +3340,7 @@
         <v>0.878</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -3356,7 +3369,7 @@
         <v>0.85699999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -3385,7 +3398,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -3414,7 +3427,7 @@
         <v>0.85699999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -3443,7 +3456,7 @@
         <v>0.876</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -3472,7 +3485,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -3501,7 +3514,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -3530,7 +3543,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -3559,7 +3572,7 @@
         <v>0.871</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -3588,7 +3601,7 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -3617,7 +3630,7 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -3646,7 +3659,7 @@
         <v>0.86899999999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -3675,7 +3688,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -3704,7 +3717,7 @@
         <v>0.88100000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -3733,7 +3746,7 @@
         <v>0.872</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -3762,7 +3775,7 @@
         <v>0.86899999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -3791,7 +3804,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -3820,7 +3833,7 @@
         <v>0.86599999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -3849,7 +3862,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -3878,7 +3891,7 @@
         <v>0.873</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -3907,7 +3920,7 @@
         <v>0.84799999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -3936,7 +3949,7 @@
         <v>0.871</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -3965,7 +3978,7 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -3994,7 +4007,7 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -4023,7 +4036,7 @@
         <v>0.86199999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -4052,7 +4065,7 @@
         <v>0.879</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -4081,7 +4094,7 @@
         <v>0.86599999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -4110,7 +4123,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -4139,7 +4152,7 @@
         <v>0.85099999999999998</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -4168,7 +4181,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -4197,7 +4210,7 @@
         <v>0.88600000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -4226,7 +4239,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -4255,7 +4268,7 @@
         <v>0.86699999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -4284,7 +4297,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -4313,7 +4326,7 @@
         <v>0.86899999999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -4342,7 +4355,7 @@
         <v>0.85099999999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -4371,7 +4384,7 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>77</v>
       </c>
@@ -4400,7 +4413,7 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>78</v>
       </c>
@@ -4429,7 +4442,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -4458,7 +4471,7 @@
         <v>0.88200000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -4487,7 +4500,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -4516,7 +4529,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>82</v>
       </c>
@@ -4545,7 +4558,7 @@
         <v>0.88500000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -4574,7 +4587,7 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -4603,7 +4616,7 @@
         <v>0.85099999999999998</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -4632,7 +4645,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>86</v>
       </c>
@@ -4661,7 +4674,7 @@
         <v>0.88600000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>87</v>
       </c>
@@ -4690,7 +4703,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>88</v>
       </c>
@@ -4719,7 +4732,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>89</v>
       </c>
@@ -4748,7 +4761,7 @@
         <v>0.86899999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>90</v>
       </c>
@@ -4777,7 +4790,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>91</v>
       </c>
@@ -4806,7 +4819,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -4835,7 +4848,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>93</v>
       </c>
@@ -4864,7 +4877,7 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>94</v>
       </c>
@@ -4893,7 +4906,7 @@
         <v>0.85499999999999998</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>95</v>
       </c>
@@ -4922,7 +4935,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>96</v>
       </c>
@@ -4951,7 +4964,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>97</v>
       </c>
@@ -4980,7 +4993,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>98</v>
       </c>
@@ -5009,7 +5022,7 @@
         <v>0.88700000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>99</v>
       </c>
@@ -5038,7 +5051,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>100</v>
       </c>
@@ -5067,7 +5080,7 @@
         <v>0.86799999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>101</v>
       </c>
@@ -5096,7 +5109,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>102</v>
       </c>
@@ -5125,7 +5138,7 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>103</v>
       </c>
@@ -5154,7 +5167,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>104</v>
       </c>
@@ -5183,7 +5196,7 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>105</v>
       </c>
@@ -5212,7 +5225,7 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>106</v>
       </c>
@@ -5241,7 +5254,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -5270,7 +5283,7 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>108</v>
       </c>
@@ -5299,7 +5312,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>109</v>
       </c>
@@ -5328,7 +5341,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>110</v>
       </c>
@@ -5357,7 +5370,7 @@
         <v>0.86699999999999999</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>111</v>
       </c>
@@ -5386,7 +5399,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>112</v>
       </c>
@@ -5415,7 +5428,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>113</v>
       </c>
@@ -5444,7 +5457,7 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -5473,7 +5486,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>115</v>
       </c>
@@ -5502,7 +5515,7 @@
         <v>0.85599999999999998</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>116</v>
       </c>
@@ -5531,7 +5544,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>117</v>
       </c>
@@ -5560,7 +5573,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>118</v>
       </c>
@@ -5589,7 +5602,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>119</v>
       </c>
@@ -5618,7 +5631,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>120</v>
       </c>
@@ -5647,7 +5660,7 @@
         <v>0.86599999999999999</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>121</v>
       </c>
@@ -5676,7 +5689,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>122</v>
       </c>
@@ -5705,7 +5718,7 @@
         <v>0.86799999999999999</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>123</v>
       </c>
@@ -5734,7 +5747,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>124</v>
       </c>
@@ -5763,7 +5776,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>125</v>
       </c>
@@ -5792,7 +5805,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>126</v>
       </c>
@@ -5821,7 +5834,7 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>127</v>
       </c>
@@ -5850,7 +5863,7 @@
         <v>0.84899999999999998</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -5879,7 +5892,7 @@
         <v>0.876</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>129</v>
       </c>
@@ -5908,7 +5921,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -5937,7 +5950,7 @@
         <v>0.85699999999999998</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>131</v>
       </c>
@@ -5966,7 +5979,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -5995,7 +6008,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -6024,7 +6037,7 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>134</v>
       </c>
@@ -6053,7 +6066,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>135</v>
       </c>
@@ -6082,7 +6095,7 @@
         <v>0.873</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>136</v>
       </c>
@@ -6111,7 +6124,7 @@
         <v>0.82399999999999995</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>137</v>
       </c>
@@ -6140,7 +6153,7 @@
         <v>0.83799999999999997</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>138</v>
       </c>
@@ -6169,7 +6182,7 @@
         <v>0.86599999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>139</v>
       </c>
@@ -6198,7 +6211,7 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>140</v>
       </c>
@@ -6227,7 +6240,7 @@
         <v>0.85599999999999998</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>141</v>
       </c>
@@ -6256,7 +6269,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>142</v>
       </c>
@@ -6285,7 +6298,7 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>143</v>
       </c>
@@ -6314,7 +6327,7 @@
         <v>0.872</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>144</v>
       </c>
@@ -6343,7 +6356,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>145</v>
       </c>
@@ -6372,7 +6385,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>146</v>
       </c>
@@ -6401,7 +6414,7 @@
         <v>0.86899999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>147</v>
       </c>
@@ -6430,7 +6443,7 @@
         <v>0.873</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>148</v>
       </c>
@@ -6459,7 +6472,7 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>149</v>
       </c>
@@ -6488,7 +6501,7 @@
         <v>0.85099999999999998</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>150</v>
       </c>
@@ -6517,7 +6530,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>151</v>
       </c>
@@ -6546,7 +6559,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>152</v>
       </c>
@@ -6575,7 +6588,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>153</v>
       </c>
@@ -6604,7 +6617,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>154</v>
       </c>
@@ -6633,7 +6646,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>155</v>
       </c>
@@ -6662,7 +6675,7 @@
         <v>0.83099999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>156</v>
       </c>
@@ -6691,7 +6704,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>157</v>
       </c>
@@ -6720,7 +6733,7 @@
         <v>0.83899999999999997</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>158</v>
       </c>
@@ -6749,7 +6762,7 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>159</v>
       </c>
@@ -6778,7 +6791,7 @@
         <v>0.82699999999999996</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>160</v>
       </c>
@@ -6807,7 +6820,7 @@
         <v>0.86699999999999999</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>161</v>
       </c>
@@ -6836,7 +6849,7 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>162</v>
       </c>
@@ -6865,7 +6878,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>163</v>
       </c>
@@ -6894,7 +6907,7 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>164</v>
       </c>
@@ -6923,7 +6936,7 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>165</v>
       </c>
@@ -6952,7 +6965,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>166</v>
       </c>
@@ -6981,7 +6994,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>167</v>
       </c>
@@ -7010,7 +7023,7 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>168</v>
       </c>
@@ -7039,7 +7052,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>169</v>
       </c>
@@ -7068,7 +7081,7 @@
         <v>0.85499999999999998</v>
       </c>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>170</v>
       </c>
@@ -7097,7 +7110,7 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>171</v>
       </c>
@@ -7126,7 +7139,7 @@
         <v>0.83899999999999997</v>
       </c>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>172</v>
       </c>
@@ -7155,7 +7168,7 @@
         <v>0.873</v>
       </c>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>173</v>
       </c>
@@ -7184,7 +7197,7 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>174</v>
       </c>
@@ -7213,7 +7226,7 @@
         <v>0.86499999999999999</v>
       </c>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>175</v>
       </c>
@@ -7242,7 +7255,7 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>176</v>
       </c>
@@ -7271,7 +7284,7 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>177</v>
       </c>
@@ -7300,7 +7313,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>178</v>
       </c>
@@ -7329,7 +7342,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>179</v>
       </c>
@@ -7358,7 +7371,7 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>180</v>
       </c>
@@ -7387,7 +7400,7 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>181</v>
       </c>
@@ -7416,7 +7429,7 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>182</v>
       </c>
@@ -7445,7 +7458,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>183</v>
       </c>
@@ -7474,7 +7487,7 @@
         <v>0.84899999999999998</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>184</v>
       </c>
@@ -7503,7 +7516,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>185</v>
       </c>
@@ -7532,7 +7545,7 @@
         <v>0.83399999999999996</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>186</v>
       </c>
@@ -7561,7 +7574,7 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>187</v>
       </c>
@@ -7590,7 +7603,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>188</v>
       </c>
@@ -7619,7 +7632,7 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>189</v>
       </c>
@@ -7648,7 +7661,7 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>190</v>
       </c>
@@ -7677,7 +7690,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>191</v>
       </c>
@@ -7706,7 +7719,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>192</v>
       </c>
@@ -7735,7 +7748,7 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>193</v>
       </c>
@@ -7764,7 +7777,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>194</v>
       </c>
@@ -7793,7 +7806,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>195</v>
       </c>
@@ -7822,7 +7835,7 @@
         <v>0.83899999999999997</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>196</v>
       </c>
@@ -7851,7 +7864,7 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>197</v>
       </c>
@@ -7880,7 +7893,7 @@
         <v>0.85699999999999998</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>198</v>
       </c>
@@ -7909,7 +7922,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>199</v>
       </c>
@@ -7938,7 +7951,7 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>200</v>
       </c>
@@ -7967,7 +7980,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>201</v>
       </c>
@@ -7996,7 +8009,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>202</v>
       </c>
@@ -8025,7 +8038,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -8054,7 +8067,7 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>204</v>
       </c>
@@ -8083,7 +8096,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>205</v>
       </c>
@@ -8112,7 +8125,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>206</v>
       </c>
@@ -8141,7 +8154,7 @@
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>207</v>
       </c>
@@ -8170,7 +8183,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>208</v>
       </c>
@@ -8199,7 +8212,7 @@
         <v>0.86599999999999999</v>
       </c>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>209</v>
       </c>
@@ -8228,7 +8241,7 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>210</v>
       </c>
@@ -8257,7 +8270,7 @@
         <v>0.83399999999999996</v>
       </c>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>211</v>
       </c>
@@ -8286,7 +8299,7 @@
         <v>0.85099999999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>212</v>
       </c>
@@ -8315,7 +8328,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>213</v>
       </c>
@@ -8344,7 +8357,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>214</v>
       </c>
@@ -8373,7 +8386,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>215</v>
       </c>
@@ -8402,7 +8415,7 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>216</v>
       </c>
@@ -8431,7 +8444,7 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>217</v>
       </c>
@@ -8460,7 +8473,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>218</v>
       </c>
@@ -8489,7 +8502,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>219</v>
       </c>
@@ -8518,7 +8531,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>220</v>
       </c>
@@ -8547,7 +8560,7 @@
         <v>0.82399999999999995</v>
       </c>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>221</v>
       </c>
@@ -8576,7 +8589,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>222</v>
       </c>
@@ -8605,7 +8618,7 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>223</v>
       </c>
@@ -8634,7 +8647,7 @@
         <v>0.86499999999999999</v>
       </c>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>224</v>
       </c>
@@ -8663,7 +8676,7 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>225</v>
       </c>
@@ -8692,7 +8705,7 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>226</v>
       </c>
@@ -8721,7 +8734,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>227</v>
       </c>
@@ -8750,7 +8763,7 @@
         <v>0.82399999999999995</v>
       </c>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>228</v>
       </c>
@@ -8779,7 +8792,7 @@
         <v>0.84799999999999998</v>
       </c>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>229</v>
       </c>
@@ -8808,7 +8821,7 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="223" spans="1:9">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>230</v>
       </c>
@@ -8837,7 +8850,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="224" spans="1:9">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>231</v>
       </c>
@@ -8866,7 +8879,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>232</v>
       </c>
@@ -8895,7 +8908,7 @@
         <v>0.82699999999999996</v>
       </c>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>233</v>
       </c>
@@ -8924,7 +8937,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>234</v>
       </c>
@@ -8953,7 +8966,7 @@
         <v>0.86099999999999999</v>
       </c>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>235</v>
       </c>
@@ -8982,7 +8995,7 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>236</v>
       </c>
@@ -9011,7 +9024,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>237</v>
       </c>
@@ -9040,7 +9053,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>238</v>
       </c>
@@ -9069,7 +9082,7 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>239</v>
       </c>
@@ -9098,7 +9111,7 @@
         <v>0.86899999999999999</v>
       </c>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>240</v>
       </c>
@@ -9127,7 +9140,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>241</v>
       </c>
@@ -9156,7 +9169,7 @@
         <v>0.86699999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>242</v>
       </c>
@@ -9185,7 +9198,7 @@
         <v>0.84799999999999998</v>
       </c>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>243</v>
       </c>
@@ -9214,7 +9227,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>244</v>
       </c>
@@ -9243,7 +9256,7 @@
         <v>0.84799999999999998</v>
       </c>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>245</v>
       </c>
@@ -9272,7 +9285,7 @@
         <v>0.83799999999999997</v>
       </c>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>246</v>
       </c>
@@ -9301,7 +9314,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>247</v>
       </c>
@@ -9330,7 +9343,7 @@
         <v>0.82699999999999996</v>
       </c>
     </row>
-    <row r="241" spans="1:9">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>248</v>
       </c>
@@ -9359,7 +9372,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="242" spans="1:9">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>249</v>
       </c>
@@ -9388,7 +9401,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="243" spans="1:9">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>250</v>
       </c>
@@ -9417,7 +9430,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:9">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>251</v>
       </c>
@@ -9446,7 +9459,7 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="245" spans="1:9">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>252</v>
       </c>
@@ -9475,7 +9488,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="246" spans="1:9">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>253</v>
       </c>
@@ -9504,7 +9517,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="247" spans="1:9">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>254</v>
       </c>
@@ -9533,7 +9546,7 @@
         <v>0.83399999999999996</v>
       </c>
     </row>
-    <row r="248" spans="1:9">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>255</v>
       </c>
@@ -9562,7 +9575,7 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="249" spans="1:9">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>256</v>
       </c>
@@ -9591,7 +9604,7 @@
         <v>0.83299999999999996</v>
       </c>
     </row>
-    <row r="250" spans="1:9">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>257</v>
       </c>
@@ -9620,7 +9633,7 @@
         <v>0.82699999999999996</v>
       </c>
     </row>
-    <row r="251" spans="1:9">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>258</v>
       </c>
@@ -9649,7 +9662,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="252" spans="1:9">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>259</v>
       </c>
@@ -9678,7 +9691,7 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="253" spans="1:9">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>260</v>
       </c>
@@ -9707,7 +9720,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="254" spans="1:9">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>261</v>
       </c>
@@ -9736,7 +9749,7 @@
         <v>0.85699999999999998</v>
       </c>
     </row>
-    <row r="255" spans="1:9">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>262</v>
       </c>
@@ -9765,7 +9778,7 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="256" spans="1:9">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>263</v>
       </c>
@@ -9794,7 +9807,7 @@
         <v>0.80800000000000005</v>
       </c>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>264</v>
       </c>
@@ -9823,7 +9836,7 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>265</v>
       </c>
@@ -9852,7 +9865,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>266</v>
       </c>
@@ -9881,7 +9894,7 @@
         <v>0.80800000000000005</v>
       </c>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>267</v>
       </c>
@@ -9910,7 +9923,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>268</v>
       </c>
@@ -9939,7 +9952,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>269</v>
       </c>
@@ -9968,7 +9981,7 @@
         <v>0.86599999999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>270</v>
       </c>
@@ -9997,7 +10010,7 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>271</v>
       </c>
@@ -10026,7 +10039,7 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>272</v>
       </c>
@@ -10055,7 +10068,7 @@
         <v>0.80400000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>273</v>
       </c>
@@ -10084,7 +10097,7 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>274</v>
       </c>
@@ -10113,7 +10126,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>275</v>
       </c>
@@ -10142,7 +10155,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>276</v>
       </c>
@@ -10171,7 +10184,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>277</v>
       </c>
@@ -10200,7 +10213,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>278</v>
       </c>
@@ -10229,7 +10242,7 @@
         <v>0.85099999999999998</v>
       </c>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>279</v>
       </c>
@@ -10258,7 +10271,7 @@
         <v>0.83399999999999996</v>
       </c>
     </row>
-    <row r="273" spans="1:9">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>280</v>
       </c>
@@ -10287,7 +10300,7 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="274" spans="1:9">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>281</v>
       </c>
@@ -10316,7 +10329,7 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="275" spans="1:9">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>282</v>
       </c>
@@ -10345,7 +10358,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="276" spans="1:9">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>283</v>
       </c>
@@ -10374,7 +10387,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="277" spans="1:9">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>284</v>
       </c>
@@ -10403,7 +10416,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="278" spans="1:9">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>285</v>
       </c>
@@ -10432,7 +10445,7 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="279" spans="1:9">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>286</v>
       </c>
@@ -10461,7 +10474,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="280" spans="1:9">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>287</v>
       </c>
@@ -10490,7 +10503,7 @@
         <v>0.84899999999999998</v>
       </c>
     </row>
-    <row r="281" spans="1:9">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>288</v>
       </c>
@@ -10519,7 +10532,7 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="282" spans="1:9">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>289</v>
       </c>
@@ -10548,7 +10561,7 @@
         <v>0.85099999999999998</v>
       </c>
     </row>
-    <row r="283" spans="1:9">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>290</v>
       </c>
@@ -10577,7 +10590,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="284" spans="1:9">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>291</v>
       </c>
@@ -10606,7 +10619,7 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="285" spans="1:9">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>292</v>
       </c>
@@ -10635,7 +10648,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="286" spans="1:9">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>293</v>
       </c>
@@ -10664,7 +10677,7 @@
         <v>0.82199999999999995</v>
       </c>
     </row>
-    <row r="287" spans="1:9">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>294</v>
       </c>
@@ -10693,7 +10706,7 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="288" spans="1:9">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>295</v>
       </c>
@@ -10722,7 +10735,7 @@
         <v>0.83099999999999996</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>296</v>
       </c>
@@ -10751,7 +10764,7 @@
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>297</v>
       </c>
@@ -10780,7 +10793,7 @@
         <v>0.80800000000000005</v>
       </c>
     </row>
-    <row r="291" spans="1:9">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>298</v>
       </c>
@@ -10809,7 +10822,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="292" spans="1:9">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>299</v>
       </c>
@@ -10838,7 +10851,7 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>300</v>
       </c>
@@ -10867,7 +10880,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="294" spans="1:9">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>301</v>
       </c>
@@ -10896,7 +10909,7 @@
         <v>0.86699999999999999</v>
       </c>
     </row>
-    <row r="295" spans="1:9">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>302</v>
       </c>
@@ -10925,7 +10938,7 @@
         <v>0.85399999999999998</v>
       </c>
     </row>
-    <row r="296" spans="1:9">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>303</v>
       </c>
@@ -10954,7 +10967,7 @@
         <v>0.81599999999999995</v>
       </c>
     </row>
-    <row r="297" spans="1:9">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>304</v>
       </c>
@@ -10983,7 +10996,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="298" spans="1:9">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>305</v>
       </c>
@@ -11012,7 +11025,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="299" spans="1:9">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>306</v>
       </c>
@@ -11041,7 +11054,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>307</v>
       </c>
@@ -11070,7 +11083,7 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>308</v>
       </c>
@@ -11099,7 +11112,7 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>309</v>
       </c>
@@ -11128,7 +11141,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="303" spans="1:9">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>310</v>
       </c>
@@ -11157,7 +11170,7 @@
         <v>0.85599999999999998</v>
       </c>
     </row>
-    <row r="304" spans="1:9">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>311</v>
       </c>
@@ -11186,7 +11199,7 @@
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="305" spans="1:9">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>312</v>
       </c>
@@ -11215,7 +11228,7 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="306" spans="1:9">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>313</v>
       </c>
@@ -11244,7 +11257,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="307" spans="1:9">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>314</v>
       </c>
@@ -11273,7 +11286,7 @@
         <v>0.85599999999999998</v>
       </c>
     </row>
-    <row r="308" spans="1:9">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>315</v>
       </c>
@@ -11302,7 +11315,7 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="309" spans="1:9">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>316</v>
       </c>
@@ -11331,7 +11344,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="310" spans="1:9">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>317</v>
       </c>
@@ -11360,7 +11373,7 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="311" spans="1:9">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>318</v>
       </c>
@@ -11389,7 +11402,7 @@
         <v>0.82399999999999995</v>
       </c>
     </row>
-    <row r="312" spans="1:9">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>319</v>
       </c>
@@ -11418,7 +11431,7 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="313" spans="1:9">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>320</v>
       </c>
@@ -11447,7 +11460,7 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="314" spans="1:9">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>321</v>
       </c>
@@ -11476,7 +11489,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="315" spans="1:9">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>322</v>
       </c>
@@ -11505,7 +11518,7 @@
         <v>0.81200000000000006</v>
       </c>
     </row>
-    <row r="316" spans="1:9">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>323</v>
       </c>
@@ -11534,7 +11547,7 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="317" spans="1:9">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>324</v>
       </c>
@@ -11563,7 +11576,7 @@
         <v>0.85099999999999998</v>
       </c>
     </row>
-    <row r="318" spans="1:9">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>325</v>
       </c>
@@ -11592,7 +11605,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="319" spans="1:9">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>326</v>
       </c>
@@ -11621,7 +11634,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="320" spans="1:9">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>327</v>
       </c>
@@ -11650,7 +11663,7 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="321" spans="1:9">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>328</v>
       </c>
@@ -11679,7 +11692,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="322" spans="1:9">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>329</v>
       </c>
@@ -11708,7 +11721,7 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="323" spans="1:9">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>330</v>
       </c>
@@ -11737,7 +11750,7 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="324" spans="1:9">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>331</v>
       </c>
@@ -11766,7 +11779,7 @@
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="325" spans="1:9">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>332</v>
       </c>
@@ -11795,7 +11808,7 @@
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="326" spans="1:9">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>333</v>
       </c>
@@ -11824,7 +11837,7 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="327" spans="1:9">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>334</v>
       </c>
@@ -11853,7 +11866,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:9">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>335</v>
       </c>
@@ -11882,7 +11895,7 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="329" spans="1:9">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>336</v>
       </c>
@@ -11911,7 +11924,7 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="330" spans="1:9">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>337</v>
       </c>
@@ -11940,7 +11953,7 @@
         <v>0.83399999999999996</v>
       </c>
     </row>
-    <row r="331" spans="1:9">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>338</v>
       </c>
@@ -11969,7 +11982,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="332" spans="1:9">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>339</v>
       </c>
@@ -11998,7 +12011,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="333" spans="1:9">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>340</v>
       </c>
@@ -12027,7 +12040,7 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="334" spans="1:9">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>341</v>
       </c>
@@ -12056,7 +12069,7 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:9">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>342</v>
       </c>
@@ -12085,7 +12098,7 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="336" spans="1:9">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>343</v>
       </c>
@@ -12114,7 +12127,7 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="337" spans="1:9">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>344</v>
       </c>
@@ -12143,7 +12156,7 @@
         <v>0.82099999999999995</v>
       </c>
     </row>
-    <row r="338" spans="1:9">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>345</v>
       </c>
@@ -12172,7 +12185,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="339" spans="1:9">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>346</v>
       </c>
@@ -12201,7 +12214,7 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="340" spans="1:9">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>347</v>
       </c>
@@ -12230,7 +12243,7 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="341" spans="1:9">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>348</v>
       </c>
@@ -12259,7 +12272,7 @@
         <v>0.873</v>
       </c>
     </row>
-    <row r="342" spans="1:9">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>349</v>
       </c>
@@ -12288,7 +12301,7 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="343" spans="1:9">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>350</v>
       </c>
@@ -12317,7 +12330,7 @@
         <v>0.86199999999999999</v>
       </c>
     </row>
-    <row r="344" spans="1:9">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>351</v>
       </c>
@@ -12346,7 +12359,7 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="345" spans="1:9">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>352</v>
       </c>
@@ -12375,7 +12388,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="346" spans="1:9">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>353</v>
       </c>
@@ -12404,7 +12417,7 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="347" spans="1:9">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>354</v>
       </c>
@@ -12433,7 +12446,7 @@
         <v>0.85499999999999998</v>
       </c>
     </row>
-    <row r="348" spans="1:9">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>355</v>
       </c>
@@ -12462,7 +12475,7 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="349" spans="1:9">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>356</v>
       </c>
@@ -12491,9 +12504,9 @@
         <v>0.82699999999999996</v>
       </c>
     </row>
-    <row r="350" spans="1:9">
-      <c r="A350" t="s">
-        <v>357</v>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A350" s="2" t="s">
+        <v>650</v>
       </c>
       <c r="B350">
         <v>897</v>
@@ -12520,9 +12533,9 @@
         <v>0.83899999999999997</v>
       </c>
     </row>
-    <row r="351" spans="1:9">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B351">
         <v>897</v>
@@ -12549,9 +12562,9 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="352" spans="1:9">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B352">
         <v>897</v>
@@ -12578,9 +12591,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="353" spans="1:9">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B353">
         <v>897</v>
@@ -12607,9 +12620,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="354" spans="1:9">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B354">
         <v>897</v>
@@ -12636,9 +12649,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="355" spans="1:9">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B355">
         <v>897</v>
@@ -12665,9 +12678,9 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="356" spans="1:9">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B356">
         <v>897</v>
@@ -12694,9 +12707,9 @@
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="357" spans="1:9">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B357">
         <v>920</v>
@@ -12723,9 +12736,9 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="358" spans="1:9">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B358">
         <v>920</v>
@@ -12752,9 +12765,9 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="359" spans="1:9">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B359">
         <v>920</v>
@@ -12781,9 +12794,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="360" spans="1:9">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B360">
         <v>920</v>
@@ -12810,9 +12823,9 @@
         <v>0.82199999999999995</v>
       </c>
     </row>
-    <row r="361" spans="1:9">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B361">
         <v>920</v>
@@ -12839,9 +12852,9 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="362" spans="1:9">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B362">
         <v>920</v>
@@ -12868,9 +12881,9 @@
         <v>0.83799999999999997</v>
       </c>
     </row>
-    <row r="363" spans="1:9">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B363">
         <v>940</v>
@@ -12897,9 +12910,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="364" spans="1:9">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B364">
         <v>940</v>
@@ -12926,9 +12939,9 @@
         <v>0.872</v>
       </c>
     </row>
-    <row r="365" spans="1:9">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B365">
         <v>940</v>
@@ -12955,9 +12968,9 @@
         <v>0.85699999999999998</v>
       </c>
     </row>
-    <row r="366" spans="1:9">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B366">
         <v>940</v>
@@ -12984,9 +12997,9 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="367" spans="1:9">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B367">
         <v>940</v>
@@ -13013,9 +13026,9 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="368" spans="1:9">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B368">
         <v>940</v>
@@ -13042,9 +13055,9 @@
         <v>0.82199999999999995</v>
       </c>
     </row>
-    <row r="369" spans="1:9">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B369">
         <v>940</v>
@@ -13071,9 +13084,9 @@
         <v>0.80400000000000005</v>
       </c>
     </row>
-    <row r="370" spans="1:9">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B370">
         <v>940</v>
@@ -13100,9 +13113,9 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="371" spans="1:9">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B371">
         <v>965</v>
@@ -13129,9 +13142,9 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="372" spans="1:9">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B372">
         <v>965</v>
@@ -13158,9 +13171,9 @@
         <v>0.84799999999999998</v>
       </c>
     </row>
-    <row r="373" spans="1:9">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B373">
         <v>965</v>
@@ -13187,9 +13200,9 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:9">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B374">
         <v>965</v>
@@ -13216,9 +13229,9 @@
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="375" spans="1:9">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B375">
         <v>965</v>
@@ -13245,9 +13258,9 @@
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="376" spans="1:9">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B376">
         <v>965</v>
@@ -13274,9 +13287,9 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="377" spans="1:9">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B377">
         <v>965</v>
@@ -13303,9 +13316,9 @@
         <v>0.86699999999999999</v>
       </c>
     </row>
-    <row r="378" spans="1:9">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B378">
         <v>965</v>
@@ -13332,9 +13345,9 @@
         <v>0.80300000000000005</v>
       </c>
     </row>
-    <row r="379" spans="1:9">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B379">
         <v>965</v>
@@ -13361,9 +13374,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="380" spans="1:9">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B380">
         <v>965</v>
@@ -13390,9 +13403,9 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="381" spans="1:9">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B381">
         <v>965</v>
@@ -13419,9 +13432,9 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="382" spans="1:9">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B382">
         <v>993</v>
@@ -13448,9 +13461,9 @@
         <v>0.82699999999999996</v>
       </c>
     </row>
-    <row r="383" spans="1:9">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B383">
         <v>993</v>
@@ -13477,9 +13490,9 @@
         <v>0.82199999999999995</v>
       </c>
     </row>
-    <row r="384" spans="1:9">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B384">
         <v>993</v>
@@ -13506,9 +13519,9 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="385" spans="1:9">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B385">
         <v>993</v>
@@ -13535,9 +13548,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="386" spans="1:9">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B386">
         <v>993</v>
@@ -13564,9 +13577,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="387" spans="1:9">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B387">
         <v>993</v>
@@ -13593,9 +13606,9 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="388" spans="1:9">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B388">
         <v>993</v>
@@ -13622,9 +13635,9 @@
         <v>0.85199999999999998</v>
       </c>
     </row>
-    <row r="389" spans="1:9">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B389">
         <v>1021</v>
@@ -13651,9 +13664,9 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="390" spans="1:9">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B390">
         <v>1021</v>
@@ -13680,9 +13693,9 @@
         <v>0.83099999999999996</v>
       </c>
     </row>
-    <row r="391" spans="1:9">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B391">
         <v>1021</v>
@@ -13709,9 +13722,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="392" spans="1:9">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B392">
         <v>1021</v>
@@ -13738,9 +13751,9 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="393" spans="1:9">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B393">
         <v>1021</v>
@@ -13767,9 +13780,9 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="394" spans="1:9">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B394">
         <v>1021</v>
@@ -13796,9 +13809,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="395" spans="1:9">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B395">
         <v>1021</v>
@@ -13825,9 +13838,9 @@
         <v>0.83899999999999997</v>
       </c>
     </row>
-    <row r="396" spans="1:9">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B396">
         <v>1021</v>
@@ -13854,9 +13867,9 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="397" spans="1:9">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B397">
         <v>1021</v>
@@ -13883,9 +13896,9 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="398" spans="1:9">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B398">
         <v>1021</v>
@@ -13912,9 +13925,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="399" spans="1:9">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B399">
         <v>1021</v>
@@ -13941,9 +13954,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="400" spans="1:9">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B400">
         <v>1021</v>
@@ -13970,9 +13983,9 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="401" spans="1:9">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B401">
         <v>1052</v>
@@ -13999,9 +14012,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="402" spans="1:9">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B402">
         <v>1052</v>
@@ -14028,9 +14041,9 @@
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="403" spans="1:9">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B403">
         <v>1052</v>
@@ -14057,9 +14070,9 @@
         <v>0.83399999999999996</v>
       </c>
     </row>
-    <row r="404" spans="1:9">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B404">
         <v>1052</v>
@@ -14086,9 +14099,9 @@
         <v>0.82099999999999995</v>
       </c>
     </row>
-    <row r="405" spans="1:9">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B405">
         <v>1052</v>
@@ -14115,9 +14128,9 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="406" spans="1:9">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B406">
         <v>1052</v>
@@ -14144,9 +14157,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="407" spans="1:9">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B407">
         <v>1052</v>
@@ -14173,9 +14186,9 @@
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="408" spans="1:9">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B408">
         <v>1052</v>
@@ -14202,9 +14215,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="409" spans="1:9">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B409">
         <v>1052</v>
@@ -14231,9 +14244,9 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="410" spans="1:9">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B410">
         <v>1081</v>
@@ -14260,9 +14273,9 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="411" spans="1:9">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B411">
         <v>1081</v>
@@ -14289,9 +14302,9 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="412" spans="1:9">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B412">
         <v>1081</v>
@@ -14318,9 +14331,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="413" spans="1:9">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B413">
         <v>1081</v>
@@ -14347,9 +14360,9 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="414" spans="1:9">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B414">
         <v>1081</v>
@@ -14376,9 +14389,9 @@
         <v>0.871</v>
       </c>
     </row>
-    <row r="415" spans="1:9">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B415">
         <v>1081</v>
@@ -14405,9 +14418,9 @@
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="416" spans="1:9">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B416">
         <v>1081</v>
@@ -14434,9 +14447,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="417" spans="1:9">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B417">
         <v>1081</v>
@@ -14463,9 +14476,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="418" spans="1:9">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B418">
         <v>1081</v>
@@ -14492,9 +14505,9 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="419" spans="1:9">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B419">
         <v>1107</v>
@@ -14521,9 +14534,9 @@
         <v>0.83799999999999997</v>
       </c>
     </row>
-    <row r="420" spans="1:9">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B420">
         <v>1107</v>
@@ -14550,9 +14563,9 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="421" spans="1:9">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B421">
         <v>1107</v>
@@ -14579,9 +14592,9 @@
         <v>0.82799999999999996</v>
       </c>
     </row>
-    <row r="422" spans="1:9">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B422">
         <v>1107</v>
@@ -14608,9 +14621,9 @@
         <v>0.79600000000000004</v>
       </c>
     </row>
-    <row r="423" spans="1:9">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B423">
         <v>1107</v>
@@ -14637,9 +14650,9 @@
         <v>0.82099999999999995</v>
       </c>
     </row>
-    <row r="424" spans="1:9">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B424">
         <v>1107</v>
@@ -14666,9 +14679,9 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="425" spans="1:9">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B425">
         <v>1107</v>
@@ -14695,9 +14708,9 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="426" spans="1:9">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B426">
         <v>1107</v>
@@ -14724,9 +14737,9 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="427" spans="1:9">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B427">
         <v>1133</v>
@@ -14753,9 +14766,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="428" spans="1:9">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B428">
         <v>1133</v>
@@ -14782,9 +14795,9 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="429" spans="1:9">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B429">
         <v>1133</v>
@@ -14811,9 +14824,9 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="430" spans="1:9">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B430">
         <v>1133</v>
@@ -14840,9 +14853,9 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="431" spans="1:9">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B431">
         <v>1154</v>
@@ -14869,9 +14882,9 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="432" spans="1:9">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B432">
         <v>1154</v>
@@ -14898,9 +14911,9 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="433" spans="1:9">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B433">
         <v>1154</v>
@@ -14927,9 +14940,9 @@
         <v>0.82099999999999995</v>
       </c>
     </row>
-    <row r="434" spans="1:9">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B434">
         <v>1154</v>
@@ -14956,9 +14969,9 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="435" spans="1:9">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B435">
         <v>1154</v>
@@ -14985,9 +14998,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="436" spans="1:9">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B436">
         <v>1154</v>
@@ -15014,9 +15027,9 @@
         <v>0.80800000000000005</v>
       </c>
     </row>
-    <row r="437" spans="1:9">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B437">
         <v>1154</v>
@@ -15043,9 +15056,9 @@
         <v>0.83799999999999997</v>
       </c>
     </row>
-    <row r="438" spans="1:9">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B438">
         <v>1154</v>
@@ -15072,9 +15085,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="439" spans="1:9">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B439">
         <v>1154</v>
@@ -15101,9 +15114,9 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="440" spans="1:9">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B440">
         <v>1154</v>
@@ -15130,9 +15143,9 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="441" spans="1:9">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B441">
         <v>1154</v>
@@ -15159,9 +15172,9 @@
         <v>0.86599999999999999</v>
       </c>
     </row>
-    <row r="442" spans="1:9">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B442">
         <v>1154</v>
@@ -15188,9 +15201,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="443" spans="1:9">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B443">
         <v>1191</v>
@@ -15217,9 +15230,9 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="444" spans="1:9">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B444">
         <v>1191</v>
@@ -15246,9 +15259,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="445" spans="1:9">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B445">
         <v>1191</v>
@@ -15275,9 +15288,9 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="446" spans="1:9">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B446">
         <v>1191</v>
@@ -15304,9 +15317,9 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="447" spans="1:9">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B447">
         <v>1217</v>
@@ -15333,9 +15346,9 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="448" spans="1:9">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B448">
         <v>1217</v>
@@ -15362,9 +15375,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="449" spans="1:9">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B449">
         <v>1217</v>
@@ -15391,9 +15404,9 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="450" spans="1:9">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B450">
         <v>1217</v>
@@ -15420,9 +15433,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="451" spans="1:9">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B451">
         <v>1217</v>
@@ -15449,9 +15462,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="452" spans="1:9">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B452">
         <v>1217</v>
@@ -15478,9 +15491,9 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="453" spans="1:9">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B453">
         <v>1244</v>
@@ -15507,9 +15520,9 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="454" spans="1:9">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B454">
         <v>1244</v>
@@ -15536,9 +15549,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="455" spans="1:9">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B455">
         <v>1244</v>
@@ -15565,9 +15578,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="456" spans="1:9">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B456">
         <v>1244</v>
@@ -15594,9 +15607,9 @@
         <v>0.79100000000000004</v>
       </c>
     </row>
-    <row r="457" spans="1:9">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B457">
         <v>1244</v>
@@ -15623,9 +15636,9 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="458" spans="1:9">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B458">
         <v>1244</v>
@@ -15652,9 +15665,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="459" spans="1:9">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B459">
         <v>1244</v>
@@ -15681,9 +15694,9 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="460" spans="1:9">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B460">
         <v>1244</v>
@@ -15710,9 +15723,9 @@
         <v>0.84899999999999998</v>
       </c>
     </row>
-    <row r="461" spans="1:9">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B461">
         <v>1266</v>
@@ -15739,9 +15752,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="462" spans="1:9">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B462">
         <v>1266</v>
@@ -15768,9 +15781,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="463" spans="1:9">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B463">
         <v>1266</v>
@@ -15797,9 +15810,9 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="464" spans="1:9">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B464">
         <v>1266</v>
@@ -15826,9 +15839,9 @@
         <v>0.80400000000000005</v>
       </c>
     </row>
-    <row r="465" spans="1:9">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B465">
         <v>1266</v>
@@ -15855,9 +15868,9 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:9">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B466">
         <v>1266</v>
@@ -15884,9 +15897,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="467" spans="1:9">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B467">
         <v>1266</v>
@@ -15913,9 +15926,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="468" spans="1:9">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B468">
         <v>1266</v>
@@ -15942,9 +15955,9 @@
         <v>0.86299999999999999</v>
       </c>
     </row>
-    <row r="469" spans="1:9">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B469">
         <v>1266</v>
@@ -15971,9 +15984,9 @@
         <v>0.84199999999999997</v>
       </c>
     </row>
-    <row r="470" spans="1:9">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B470">
         <v>1301</v>
@@ -16000,9 +16013,9 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="471" spans="1:9">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B471">
         <v>1301</v>
@@ -16029,9 +16042,9 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="472" spans="1:9">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B472">
         <v>1301</v>
@@ -16058,9 +16071,9 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="473" spans="1:9">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B473">
         <v>1301</v>
@@ -16087,9 +16100,9 @@
         <v>0.81200000000000006</v>
       </c>
     </row>
-    <row r="474" spans="1:9">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B474">
         <v>1301</v>
@@ -16116,9 +16129,9 @@
         <v>0.85099999999999998</v>
       </c>
     </row>
-    <row r="475" spans="1:9">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B475">
         <v>1301</v>
@@ -16145,9 +16158,9 @@
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="476" spans="1:9">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B476">
         <v>1301</v>
@@ -16174,9 +16187,9 @@
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="477" spans="1:9">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B477">
         <v>1331</v>
@@ -16203,9 +16216,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="478" spans="1:9">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B478">
         <v>1331</v>
@@ -16232,9 +16245,9 @@
         <v>0.82699999999999996</v>
       </c>
     </row>
-    <row r="479" spans="1:9">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B479">
         <v>1331</v>
@@ -16261,9 +16274,9 @@
         <v>0.81599999999999995</v>
       </c>
     </row>
-    <row r="480" spans="1:9">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B480">
         <v>1331</v>
@@ -16290,9 +16303,9 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="481" spans="1:9">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B481">
         <v>1331</v>
@@ -16319,9 +16332,9 @@
         <v>0.82399999999999995</v>
       </c>
     </row>
-    <row r="482" spans="1:9">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B482">
         <v>1331</v>
@@ -16348,9 +16361,9 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="483" spans="1:9">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B483">
         <v>1331</v>
@@ -16377,9 +16390,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="484" spans="1:9">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B484">
         <v>1331</v>
@@ -16406,9 +16419,9 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="485" spans="1:9">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B485">
         <v>1331</v>
@@ -16435,9 +16448,9 @@
         <v>0.80300000000000005</v>
       </c>
     </row>
-    <row r="486" spans="1:9">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B486">
         <v>1331</v>
@@ -16464,9 +16477,9 @@
         <v>0.85299999999999998</v>
       </c>
     </row>
-    <row r="487" spans="1:9">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B487">
         <v>1331</v>
@@ -16493,9 +16506,9 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="488" spans="1:9">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B488">
         <v>1331</v>
@@ -16522,9 +16535,9 @@
         <v>0.82199999999999995</v>
       </c>
     </row>
-    <row r="489" spans="1:9">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B489">
         <v>1331</v>
@@ -16551,9 +16564,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="490" spans="1:9">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B490">
         <v>1362</v>
@@ -16580,9 +16593,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="491" spans="1:9">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B491">
         <v>1362</v>
@@ -16609,9 +16622,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="492" spans="1:9">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B492">
         <v>1362</v>
@@ -16638,9 +16651,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="493" spans="1:9">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B493">
         <v>1362</v>
@@ -16667,9 +16680,9 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="494" spans="1:9">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B494">
         <v>1362</v>
@@ -16696,9 +16709,9 @@
         <v>0.83899999999999997</v>
       </c>
     </row>
-    <row r="495" spans="1:9">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B495">
         <v>1398</v>
@@ -16725,9 +16738,9 @@
         <v>0.83899999999999997</v>
       </c>
     </row>
-    <row r="496" spans="1:9">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B496">
         <v>1398</v>
@@ -16754,9 +16767,9 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="497" spans="1:9">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B497">
         <v>1398</v>
@@ -16783,9 +16796,9 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="498" spans="1:9">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B498">
         <v>1398</v>
@@ -16812,9 +16825,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="499" spans="1:9">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B499">
         <v>1398</v>
@@ -16841,9 +16854,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="500" spans="1:9">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B500">
         <v>1398</v>
@@ -16870,9 +16883,9 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="501" spans="1:9">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B501">
         <v>1427</v>
@@ -16899,9 +16912,9 @@
         <v>0.84799999999999998</v>
       </c>
     </row>
-    <row r="502" spans="1:9">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B502">
         <v>1427</v>
@@ -16928,9 +16941,9 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="503" spans="1:9">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B503">
         <v>1454</v>
@@ -16957,9 +16970,9 @@
         <v>0.80700000000000005</v>
       </c>
     </row>
-    <row r="504" spans="1:9">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B504">
         <v>1454</v>
@@ -16986,9 +16999,9 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="505" spans="1:9">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B505">
         <v>1454</v>
@@ -17015,9 +17028,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="506" spans="1:9">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B506">
         <v>1454</v>
@@ -17044,9 +17057,9 @@
         <v>0.80700000000000005</v>
       </c>
     </row>
-    <row r="507" spans="1:9">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B507">
         <v>1454</v>
@@ -17073,9 +17086,9 @@
         <v>0.85799999999999998</v>
       </c>
     </row>
-    <row r="508" spans="1:9">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B508">
         <v>1454</v>
@@ -17102,9 +17115,9 @@
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="509" spans="1:9">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B509">
         <v>1454</v>
@@ -17131,9 +17144,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="510" spans="1:9">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B510">
         <v>1486</v>
@@ -17160,9 +17173,9 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="511" spans="1:9">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B511">
         <v>1486</v>
@@ -17189,9 +17202,9 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="512" spans="1:9">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B512">
         <v>1486</v>
@@ -17218,9 +17231,9 @@
         <v>0.82899999999999996</v>
       </c>
     </row>
-    <row r="513" spans="1:9">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B513">
         <v>1486</v>
@@ -17247,9 +17260,9 @@
         <v>0.80400000000000005</v>
       </c>
     </row>
-    <row r="514" spans="1:9">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B514">
         <v>1486</v>
@@ -17276,9 +17289,9 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="515" spans="1:9">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B515">
         <v>1486</v>
@@ -17305,9 +17318,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="516" spans="1:9">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B516">
         <v>1514</v>
@@ -17334,9 +17347,9 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="517" spans="1:9">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B517">
         <v>1514</v>
@@ -17363,9 +17376,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="518" spans="1:9">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B518">
         <v>1514</v>
@@ -17392,9 +17405,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="519" spans="1:9">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B519">
         <v>1514</v>
@@ -17421,9 +17434,9 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="520" spans="1:9">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B520">
         <v>1514</v>
@@ -17450,9 +17463,9 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="521" spans="1:9">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B521">
         <v>1514</v>
@@ -17479,9 +17492,9 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="522" spans="1:9">
-      <c r="A522" t="s">
-        <v>529</v>
+    <row r="522" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A522" s="2" t="s">
+        <v>651</v>
       </c>
       <c r="B522">
         <v>1514</v>
@@ -17508,9 +17521,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="523" spans="1:9">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B523">
         <v>1546</v>
@@ -17537,9 +17550,9 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="524" spans="1:9">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B524">
         <v>1546</v>
@@ -17566,9 +17579,9 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="525" spans="1:9">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B525">
         <v>1546</v>
@@ -17595,9 +17608,9 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="526" spans="1:9">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B526">
         <v>1546</v>
@@ -17624,9 +17637,9 @@
         <v>0.83899999999999997</v>
       </c>
     </row>
-    <row r="527" spans="1:9">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B527">
         <v>1546</v>
@@ -17653,9 +17666,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:9">
-      <c r="A528" t="s">
-        <v>535</v>
+    <row r="528" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A528" s="2" t="s">
+        <v>652</v>
       </c>
       <c r="B528">
         <v>1546</v>
@@ -17682,9 +17695,9 @@
         <v>0.79500000000000004</v>
       </c>
     </row>
-    <row r="529" spans="1:9">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B529">
         <v>1574</v>
@@ -17711,9 +17724,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="530" spans="1:9">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B530">
         <v>1574</v>
@@ -17740,9 +17753,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="531" spans="1:9">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B531">
         <v>1574</v>
@@ -17769,9 +17782,9 @@
         <v>0.84499999999999997</v>
       </c>
     </row>
-    <row r="532" spans="1:9">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B532">
         <v>1574</v>
@@ -17798,9 +17811,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="533" spans="1:9">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B533">
         <v>1574</v>
@@ -17827,9 +17840,9 @@
         <v>0.85499999999999998</v>
       </c>
     </row>
-    <row r="534" spans="1:9">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B534">
         <v>1574</v>
@@ -17856,9 +17869,9 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="535" spans="1:9">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B535">
         <v>1595</v>
@@ -17885,9 +17898,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="536" spans="1:9">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B536">
         <v>1595</v>
@@ -17914,9 +17927,9 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="537" spans="1:9">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B537">
         <v>1595</v>
@@ -17943,9 +17956,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="538" spans="1:9">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B538">
         <v>1595</v>
@@ -17972,9 +17985,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="539" spans="1:9">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B539">
         <v>1595</v>
@@ -18001,9 +18014,9 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="540" spans="1:9">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B540">
         <v>1595</v>
@@ -18030,9 +18043,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="541" spans="1:9">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B541">
         <v>1595</v>
@@ -18059,9 +18072,9 @@
         <v>0.79900000000000004</v>
       </c>
     </row>
-    <row r="542" spans="1:9">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B542">
         <v>1595</v>
@@ -18088,9 +18101,9 @@
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="543" spans="1:9">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B543">
         <v>1638</v>
@@ -18117,9 +18130,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="544" spans="1:9">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B544">
         <v>1638</v>
@@ -18146,9 +18159,9 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="545" spans="1:9">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B545">
         <v>1638</v>
@@ -18175,9 +18188,9 @@
         <v>0.79100000000000004</v>
       </c>
     </row>
-    <row r="546" spans="1:9">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B546">
         <v>1638</v>
@@ -18204,9 +18217,9 @@
         <v>0.81200000000000006</v>
       </c>
     </row>
-    <row r="547" spans="1:9">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B547">
         <v>1665</v>
@@ -18233,9 +18246,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="548" spans="1:9">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B548">
         <v>1665</v>
@@ -18262,9 +18275,9 @@
         <v>0.82699999999999996</v>
       </c>
     </row>
-    <row r="549" spans="1:9">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B549">
         <v>1696</v>
@@ -18291,9 +18304,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="550" spans="1:9">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B550">
         <v>1696</v>
@@ -18320,9 +18333,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="551" spans="1:9">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B551">
         <v>1720</v>
@@ -18349,9 +18362,9 @@
         <v>0.80400000000000005</v>
       </c>
     </row>
-    <row r="552" spans="1:9">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B552">
         <v>1720</v>
@@ -18378,9 +18391,9 @@
         <v>0.82399999999999995</v>
       </c>
     </row>
-    <row r="553" spans="1:9">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B553">
         <v>1720</v>
@@ -18407,9 +18420,9 @@
         <v>0.84099999999999997</v>
       </c>
     </row>
-    <row r="554" spans="1:9">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B554">
         <v>1720</v>
@@ -18436,9 +18449,9 @@
         <v>0.81200000000000006</v>
       </c>
     </row>
-    <row r="555" spans="1:9">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B555">
         <v>1756</v>
@@ -18465,9 +18478,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="556" spans="1:9">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B556">
         <v>1756</v>
@@ -18494,9 +18507,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="557" spans="1:9">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B557">
         <v>1756</v>
@@ -18523,9 +18536,9 @@
         <v>0.80700000000000005</v>
       </c>
     </row>
-    <row r="558" spans="1:9">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B558">
         <v>1756</v>
@@ -18552,9 +18565,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="559" spans="1:9">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B559">
         <v>1756</v>
@@ -18581,9 +18594,9 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="560" spans="1:9">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B560">
         <v>1756</v>
@@ -18610,9 +18623,9 @@
         <v>0.82099999999999995</v>
       </c>
     </row>
-    <row r="561" spans="1:9">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B561">
         <v>1776</v>
@@ -18639,9 +18652,9 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="562" spans="1:9">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B562">
         <v>1776</v>
@@ -18668,9 +18681,9 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="563" spans="1:9">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B563">
         <v>1776</v>
@@ -18697,9 +18710,9 @@
         <v>0.79700000000000004</v>
       </c>
     </row>
-    <row r="564" spans="1:9">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B564">
         <v>1776</v>
@@ -18726,9 +18739,9 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="565" spans="1:9">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B565">
         <v>1776</v>
@@ -18755,9 +18768,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="566" spans="1:9">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B566">
         <v>1811</v>
@@ -18784,9 +18797,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="567" spans="1:9">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B567">
         <v>1811</v>
@@ -18813,9 +18826,9 @@
         <v>0.81599999999999995</v>
       </c>
     </row>
-    <row r="568" spans="1:9">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B568">
         <v>1811</v>
@@ -18842,9 +18855,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="569" spans="1:9">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B569">
         <v>1811</v>
@@ -18871,9 +18884,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="570" spans="1:9">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B570">
         <v>1811</v>
@@ -18900,9 +18913,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="571" spans="1:9">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B571">
         <v>1811</v>
@@ -18929,9 +18942,9 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="572" spans="1:9">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B572">
         <v>1811</v>
@@ -18958,9 +18971,9 @@
         <v>0.86399999999999999</v>
       </c>
     </row>
-    <row r="573" spans="1:9">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B573">
         <v>1811</v>
@@ -18987,9 +19000,9 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="574" spans="1:9">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B574">
         <v>1811</v>
@@ -19016,9 +19029,9 @@
         <v>0.80300000000000005</v>
       </c>
     </row>
-    <row r="575" spans="1:9">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B575">
         <v>1842</v>
@@ -19045,9 +19058,9 @@
         <v>0.81499999999999995</v>
       </c>
     </row>
-    <row r="576" spans="1:9">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B576">
         <v>1842</v>
@@ -19074,9 +19087,9 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="577" spans="1:9">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B577">
         <v>1842</v>
@@ -19103,9 +19116,9 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="578" spans="1:9">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B578">
         <v>1842</v>
@@ -19132,9 +19145,9 @@
         <v>0.83799999999999997</v>
       </c>
     </row>
-    <row r="579" spans="1:9">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B579">
         <v>1866</v>
@@ -19161,9 +19174,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="580" spans="1:9">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B580">
         <v>1866</v>
@@ -19190,9 +19203,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="581" spans="1:9">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B581">
         <v>1866</v>
@@ -19219,9 +19232,9 @@
         <v>0.79800000000000004</v>
       </c>
     </row>
-    <row r="582" spans="1:9">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B582">
         <v>1904</v>
@@ -19248,9 +19261,9 @@
         <v>0.81699999999999995</v>
       </c>
     </row>
-    <row r="583" spans="1:9">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B583">
         <v>1904</v>
@@ -19277,9 +19290,9 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="584" spans="1:9">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B584">
         <v>1904</v>
@@ -19306,9 +19319,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="585" spans="1:9">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B585">
         <v>1934</v>
@@ -19335,9 +19348,9 @@
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="586" spans="1:9">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B586">
         <v>1934</v>
@@ -19364,9 +19377,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="587" spans="1:9">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B587">
         <v>1934</v>
@@ -19393,9 +19406,9 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="588" spans="1:9">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="B588">
         <v>1934</v>
@@ -19422,9 +19435,9 @@
         <v>0.82399999999999995</v>
       </c>
     </row>
-    <row r="589" spans="1:9">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B589">
         <v>1934</v>
@@ -19451,9 +19464,9 @@
         <v>0.83899999999999997</v>
       </c>
     </row>
-    <row r="590" spans="1:9">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B590">
         <v>1969</v>
@@ -19480,9 +19493,9 @@
         <v>0.79700000000000004</v>
       </c>
     </row>
-    <row r="591" spans="1:9">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B591">
         <v>1995</v>
@@ -19509,9 +19522,9 @@
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="592" spans="1:9">
-      <c r="A592" t="s">
-        <v>599</v>
+    <row r="592" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A592" s="2" t="s">
+        <v>653</v>
       </c>
       <c r="B592">
         <v>1995</v>
@@ -19538,9 +19551,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="593" spans="1:9">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B593">
         <v>1995</v>
@@ -19567,9 +19580,9 @@
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="594" spans="1:9">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B594">
         <v>1995</v>
@@ -19596,9 +19609,9 @@
         <v>0.80300000000000005</v>
       </c>
     </row>
-    <row r="595" spans="1:9">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B595">
         <v>1995</v>
@@ -19625,9 +19638,9 @@
         <v>0.80800000000000005</v>
       </c>
     </row>
-    <row r="596" spans="1:9">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B596">
         <v>1995</v>
@@ -19654,9 +19667,9 @@
         <v>0.80300000000000005</v>
       </c>
     </row>
-    <row r="597" spans="1:9">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B597">
         <v>2028</v>
@@ -19683,9 +19696,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="598" spans="1:9">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B598">
         <v>2028</v>
@@ -19712,9 +19725,9 @@
         <v>0.81899999999999995</v>
       </c>
     </row>
-    <row r="599" spans="1:9">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B599">
         <v>2028</v>
@@ -19741,9 +19754,9 @@
         <v>0.81200000000000006</v>
       </c>
     </row>
-    <row r="600" spans="1:9">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B600">
         <v>2059</v>
@@ -19770,9 +19783,9 @@
         <v>0.82299999999999995</v>
       </c>
     </row>
-    <row r="601" spans="1:9">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B601">
         <v>2059</v>
@@ -19799,9 +19812,9 @@
         <v>0.82199999999999995</v>
       </c>
     </row>
-    <row r="602" spans="1:9">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B602">
         <v>2078</v>
@@ -19828,9 +19841,9 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="603" spans="1:9">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B603">
         <v>2078</v>
@@ -19857,9 +19870,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="604" spans="1:9">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B604">
         <v>2105</v>
@@ -19886,9 +19899,9 @@
         <v>0.80300000000000005</v>
       </c>
     </row>
-    <row r="605" spans="1:9">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B605">
         <v>2105</v>
@@ -19915,9 +19928,9 @@
         <v>0.84399999999999997</v>
       </c>
     </row>
-    <row r="606" spans="1:9">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B606">
         <v>2105</v>
@@ -19944,9 +19957,9 @@
         <v>0.79700000000000004</v>
       </c>
     </row>
-    <row r="607" spans="1:9">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B607">
         <v>2134</v>
@@ -19973,9 +19986,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="608" spans="1:9">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B608">
         <v>2161</v>
@@ -20002,9 +20015,9 @@
         <v>0.84699999999999998</v>
       </c>
     </row>
-    <row r="609" spans="1:9">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B609">
         <v>2182</v>
@@ -20031,9 +20044,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="610" spans="1:9">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B610">
         <v>2182</v>
@@ -20060,9 +20073,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="611" spans="1:9">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B611">
         <v>2224</v>
@@ -20089,9 +20102,9 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="612" spans="1:9">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B612">
         <v>2224</v>
@@ -20118,9 +20131,9 @@
         <v>0.79400000000000004</v>
       </c>
     </row>
-    <row r="613" spans="1:9">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B613">
         <v>2251</v>
@@ -20147,9 +20160,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="614" spans="1:9">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B614">
         <v>2251</v>
@@ -20176,9 +20189,9 @@
         <v>0.80500000000000005</v>
       </c>
     </row>
-    <row r="615" spans="1:9">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B615">
         <v>2282</v>
@@ -20205,9 +20218,9 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="616" spans="1:9">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B616">
         <v>2282</v>
@@ -20234,9 +20247,9 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="617" spans="1:9">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B617">
         <v>2309</v>
@@ -20263,9 +20276,9 @@
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="618" spans="1:9">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B618">
         <v>2332</v>
@@ -20292,9 +20305,9 @@
         <v>0.82599999999999996</v>
       </c>
     </row>
-    <row r="619" spans="1:9">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B619">
         <v>2332</v>
@@ -20321,9 +20334,9 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="620" spans="1:9">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B620">
         <v>2412</v>
@@ -20350,9 +20363,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="621" spans="1:9">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B621">
         <v>2412</v>
@@ -20379,9 +20392,9 @@
         <v>0.84599999999999997</v>
       </c>
     </row>
-    <row r="622" spans="1:9">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B622">
         <v>2439</v>
@@ -20408,9 +20421,9 @@
         <v>0.78700000000000003</v>
       </c>
     </row>
-    <row r="623" spans="1:9">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B623">
         <v>2439</v>
@@ -20437,9 +20450,9 @@
         <v>0.79100000000000004</v>
       </c>
     </row>
-    <row r="624" spans="1:9">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B624">
         <v>2439</v>
@@ -20466,9 +20479,9 @@
         <v>0.81200000000000006</v>
       </c>
     </row>
-    <row r="625" spans="1:9">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B625">
         <v>2462</v>
@@ -20495,9 +20508,9 @@
         <v>0.81100000000000005</v>
       </c>
     </row>
-    <row r="626" spans="1:9">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B626">
         <v>2481</v>
@@ -20524,9 +20537,9 @@
         <v>0.81799999999999995</v>
       </c>
     </row>
-    <row r="627" spans="1:9">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B627">
         <v>2481</v>
@@ -20553,9 +20566,9 @@
         <v>0.82199999999999995</v>
       </c>
     </row>
-    <row r="628" spans="1:9">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B628">
         <v>2481</v>
@@ -20582,9 +20595,9 @@
         <v>0.81200000000000006</v>
       </c>
     </row>
-    <row r="629" spans="1:9">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B629">
         <v>2503</v>
@@ -20611,9 +20624,9 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="630" spans="1:9">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B630">
         <v>2503</v>
@@ -20640,9 +20653,9 @@
         <v>0.79600000000000004</v>
       </c>
     </row>
-    <row r="631" spans="1:9">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B631">
         <v>2503</v>
@@ -20669,9 +20682,9 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="632" spans="1:9">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B632">
         <v>2545</v>
@@ -20698,9 +20711,9 @@
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="633" spans="1:9">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B633">
         <v>2573</v>
@@ -20727,9 +20740,9 @@
         <v>0.84799999999999998</v>
       </c>
     </row>
-    <row r="634" spans="1:9">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B634">
         <v>2598</v>
@@ -20756,9 +20769,9 @@
         <v>0.83199999999999996</v>
       </c>
     </row>
-    <row r="635" spans="1:9">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B635">
         <v>2691</v>
@@ -20785,9 +20798,9 @@
         <v>0.80900000000000005</v>
       </c>
     </row>
-    <row r="636" spans="1:9">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B636">
         <v>2716</v>
@@ -20814,9 +20827,9 @@
         <v>0.79400000000000004</v>
       </c>
     </row>
-    <row r="637" spans="1:9">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B637">
         <v>2738</v>
@@ -20843,9 +20856,9 @@
         <v>0.79900000000000004</v>
       </c>
     </row>
-    <row r="638" spans="1:9">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B638">
         <v>2802</v>
@@ -20872,9 +20885,9 @@
         <v>0.79900000000000004</v>
       </c>
     </row>
-    <row r="639" spans="1:9">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B639">
         <v>2870</v>
@@ -20901,9 +20914,9 @@
         <v>0.81599999999999995</v>
       </c>
     </row>
-    <row r="640" spans="1:9">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B640">
         <v>2898</v>
@@ -20930,9 +20943,9 @@
         <v>0.77900000000000003</v>
       </c>
     </row>
-    <row r="641" spans="1:9">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B641">
         <v>2898</v>
@@ -20959,9 +20972,9 @@
         <v>0.77500000000000002</v>
       </c>
     </row>
-    <row r="642" spans="1:9">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B642">
         <v>2964</v>
@@ -20988,9 +21001,9 @@
         <v>0.79900000000000004</v>
       </c>
     </row>
-    <row r="643" spans="1:9">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B643">
         <v>3008</v>
@@ -21017,9 +21030,9 @@
         <v>0.81399999999999995</v>
       </c>
     </row>
-    <row r="644" spans="1:9">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B644">
         <v>3090</v>
@@ -21046,9 +21059,9 @@
         <v>0.79900000000000004</v>
       </c>
     </row>
-    <row r="645" spans="1:9">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B645">
         <v>3275</v>
@@ -21075,9 +21088,9 @@
         <v>0.79200000000000004</v>
       </c>
     </row>
-    <row r="646" spans="1:9">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B646">
         <v>3312</v>
@@ -21111,6 +21124,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F877905DB0D2DD4DB06990C75DC9A361" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="50d895277f322d891fa2f616b702e438">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="90121372-7411-44e9-a0b4-d98e677814c9" xmlns:ns3="c5531305-e480-42b6-a1a7-544f1160e8db" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="362ec418228fc2ed7f9a487db1e3a7fa" ns2:_="" ns3:_="">
     <xsd:import namespace="90121372-7411-44e9-a0b4-d98e677814c9"/>
@@ -21299,15 +21321,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -21320,13 +21333,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{490B00F7-C20F-4656-ACBE-69B740224C36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34F2A063-D0EF-41A7-A3A7-9514D6C854EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34F2A063-D0EF-41A7-A3A7-9514D6C854EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{490B00F7-C20F-4656-ACBE-69B740224C36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="90121372-7411-44e9-a0b4-d98e677814c9"/>
+    <ds:schemaRef ds:uri="c5531305-e480-42b6-a1a7-544f1160e8db"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1F3F2D6-C22C-423C-B2DD-0DB42AF6E0F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1F3F2D6-C22C-423C-B2DD-0DB42AF6E0F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="90121372-7411-44e9-a0b4-d98e677814c9"/>
+    <ds:schemaRef ds:uri="c5531305-e480-42b6-a1a7-544f1160e8db"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>